--- a/outputs/excel-templates/import_sinh_vien.xlsx
+++ b/outputs/excel-templates/import_sinh_vien.xlsx
@@ -79,7 +79,7 @@
     <t>1 Vo Van Ngan, Thu Duc</t>
   </si>
   <si>
-    <t>Dang hoc</t>
+    <t>?ang h?c</t>
   </si>
   <si>
     <t>25990002</t>
@@ -88,7 +88,7 @@
     <t>Tran Thi Mau</t>
   </si>
   <si>
-    <t>Nu</t>
+    <t>N?</t>
   </si>
   <si>
     <t>079205000002</t>
@@ -693,6 +693,6 @@
   </sheetData>
   <autoFilter ref="A1:L1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/outputs/excel-templates/import_sinh_vien.xlsx
+++ b/outputs/excel-templates/import_sinh_vien.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8DB972-4161-4DBE-97E4-6C42655B3890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Du lieu" state="visible" r:id="rId4"/>
+    <sheet name="Du lieu" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
   <si>
     <t>MSSV</t>
   </si>
@@ -49,24 +53,12 @@
     <t>TrangThai</t>
   </si>
   <si>
-    <t>25990001</t>
-  </si>
-  <si>
     <t>Nguyen Van Mau</t>
   </si>
   <si>
     <t>Nam</t>
   </si>
   <si>
-    <t>079205000001</t>
-  </si>
-  <si>
-    <t>25990001@student.uit.edu.vn</t>
-  </si>
-  <si>
-    <t>0912345601</t>
-  </si>
-  <si>
     <t>KTPM</t>
   </si>
   <si>
@@ -79,18 +71,12 @@
     <t>1 Vo Van Ngan, Thu Duc</t>
   </si>
   <si>
-    <t>?ang h?c</t>
-  </si>
-  <si>
     <t>25990002</t>
   </si>
   <si>
     <t>Tran Thi Mau</t>
   </si>
   <si>
-    <t>N?</t>
-  </si>
-  <si>
     <t>079205000002</t>
   </si>
   <si>
@@ -119,25 +105,47 @@
   </si>
   <si>
     <t>3 Vo Van Ngan, Thu Duc</t>
+  </si>
+  <si>
+    <t>Đang học</t>
+  </si>
+  <si>
+    <t>Nữ</t>
+  </si>
+  <si>
+    <t>0912345622</t>
+  </si>
+  <si>
+    <t>079205000011</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -162,10 +170,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -183,8 +192,15 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -521,9 +537,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -538,7 +554,7 @@
     <col min="12" max="12" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -576,123 +592,126 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <v>25990043</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>12</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>13</v>
       </c>
       <c r="C2" s="6">
         <v>38366.708333333336</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="L2" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="B3" s="5" t="s">
         <v>19</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="C3" s="6">
         <v>38430.708333333336</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>31</v>
       </c>
       <c r="C4" s="6">
         <v>38512.708333333336</v>
       </c>
       <c r="D4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="I4" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{36E15FDE-83AD-425A-889F-B602F1A32025}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>